--- a/KyrgyzTestFrontend/public/templates/Шаблон_импорта_сертификатов.xlsx
+++ b/KyrgyzTestFrontend/public/templates/Шаблон_импорта_сертификатов.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\KT\KyrgyzTest\KyrgyzTest\KyrgyzTestFrontend\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F05986-6919-4616-B40E-FC94F215FFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9582520E-F6F4-4A6F-9F55-8DCFA45545E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -135,9 +135,6 @@
     <t>Сертификаттын берилген күнү</t>
   </si>
   <si>
-    <t>Эскертүү</t>
-  </si>
-  <si>
     <t>КАК ЗАПОЛНЯТЬ ФАЙЛ</t>
   </si>
   <si>
@@ -160,6 +157,9 @@
   </si>
   <si>
     <t>7. Не объединяйте ячейки и не вставляйте несколько записей в одну строку.</t>
+  </si>
+  <si>
+    <t>Комментарии</t>
   </si>
 </sst>
 </file>
@@ -620,7 +620,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2237,42 +2237,42 @@
   <sheetData>
     <row r="1" spans="1:1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
